--- a/metadata/donors/simple_donor_meta1.xlsx
+++ b/metadata/donors/simple_donor_meta1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/michaeltisza/mike_tisza/github_repos/ogb_brain_virome_analysis/metadata/donors/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67E9AFEC-2386-4E40-8E4E-A4E623694726}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{557B746F-D1AC-354C-99EE-DE735629BC23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="58740" yWindow="3540" windowWidth="22700" windowHeight="15720" xr2:uid="{5189DBCA-FE73-974C-A372-1536F7AE4D0C}"/>
+    <workbookView xWindow="45700" yWindow="1440" windowWidth="16440" windowHeight="16060" xr2:uid="{5189DBCA-FE73-974C-A372-1536F7AE4D0C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,10 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="174">
-  <si>
-    <t>year_patient</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="218">
   <si>
     <t>AD_status</t>
   </si>
@@ -561,6 +558,141 @@
   </si>
   <si>
     <t>H-HCTZZRA018</t>
+  </si>
+  <si>
+    <t>2008-73</t>
+  </si>
+  <si>
+    <t>2011-13</t>
+  </si>
+  <si>
+    <t>2012-76</t>
+  </si>
+  <si>
+    <t>2014-33</t>
+  </si>
+  <si>
+    <t>08-143</t>
+  </si>
+  <si>
+    <t>11-135</t>
+  </si>
+  <si>
+    <t>16-021</t>
+  </si>
+  <si>
+    <t>00-120</t>
+  </si>
+  <si>
+    <t>00-171</t>
+  </si>
+  <si>
+    <t>00-180</t>
+  </si>
+  <si>
+    <t>00-198</t>
+  </si>
+  <si>
+    <t>00-209</t>
+  </si>
+  <si>
+    <t>01-006</t>
+  </si>
+  <si>
+    <t>01-169</t>
+  </si>
+  <si>
+    <t>02-020</t>
+  </si>
+  <si>
+    <t>99-058</t>
+  </si>
+  <si>
+    <t>99-113</t>
+  </si>
+  <si>
+    <t>03-119</t>
+  </si>
+  <si>
+    <t>06-045</t>
+  </si>
+  <si>
+    <t>14-150</t>
+  </si>
+  <si>
+    <t>13-045</t>
+  </si>
+  <si>
+    <t>11-043</t>
+  </si>
+  <si>
+    <t>02-187</t>
+  </si>
+  <si>
+    <t>03-077</t>
+  </si>
+  <si>
+    <t>03-120</t>
+  </si>
+  <si>
+    <t>03-123</t>
+  </si>
+  <si>
+    <t>03-164</t>
+  </si>
+  <si>
+    <t>15-173</t>
+  </si>
+  <si>
+    <t>15-142</t>
+  </si>
+  <si>
+    <t>A14-00037</t>
+  </si>
+  <si>
+    <t>A14-00040</t>
+  </si>
+  <si>
+    <t>A14-00041</t>
+  </si>
+  <si>
+    <t>02-203</t>
+  </si>
+  <si>
+    <t>06-066</t>
+  </si>
+  <si>
+    <t>14-131</t>
+  </si>
+  <si>
+    <t>10-160</t>
+  </si>
+  <si>
+    <t>15-00084</t>
+  </si>
+  <si>
+    <t>14-132</t>
+  </si>
+  <si>
+    <t>14-54</t>
+  </si>
+  <si>
+    <t>13-138</t>
+  </si>
+  <si>
+    <t>A14-00047</t>
+  </si>
+  <si>
+    <t>A14-00095</t>
+  </si>
+  <si>
+    <t>06-150</t>
+  </si>
+  <si>
+    <t>join_col</t>
+  </si>
+  <si>
+    <t>patient_ID</t>
   </si>
 </sst>
 </file>
@@ -619,7 +751,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -633,6 +765,7 @@
     <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -968,1903 +1101,2405 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72A9D7AE-91AD-2F46-8F2D-3CA72A578168}">
-  <dimension ref="A1:C172"/>
+  <dimension ref="A1:D171"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="B2" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2" s="4">
         <v>85</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D2" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3" s="4">
         <v>75</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D3" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C4" s="4">
         <v>84</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D4" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" s="4">
         <v>74</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D5" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C6" s="4">
         <v>85</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D6" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C7" s="4">
         <v>86</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D7" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C8" s="4">
         <v>78</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D8" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9" s="4">
         <v>82</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D9" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" s="4">
         <v>82</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D10" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" s="4">
         <v>81</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D11" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C12" s="4">
         <v>86</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D12" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C13" s="4">
         <v>79</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D13" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C14" s="4">
         <v>77</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D14" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" s="4">
         <v>81</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D15" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C16" s="4">
         <v>76</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D16" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C17" s="4">
         <v>79</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D17" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C18" s="4">
         <v>75</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D18" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C19" s="4">
         <v>86</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D19" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C20" s="4">
         <v>83</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D20" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C21" s="4">
         <v>85</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D21" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C22" s="4">
         <v>81</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D22" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C23" s="4">
         <v>78</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D23" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C24" s="4">
         <v>72</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D24" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C25" s="4">
         <v>78</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D25" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C26" s="4">
         <v>79</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D26" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C27" s="4">
         <v>75</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D27" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C28" s="4">
         <v>79</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D28" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C29" s="4">
         <v>79</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D29" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C30" s="4">
         <v>74</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D30" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C31" s="4">
         <v>82</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D31" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C32" s="4">
         <v>70</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D32" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C33" s="4">
         <v>77</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D33" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C34" s="4">
         <v>75</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D34" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C35" s="4">
         <v>72</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D35" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C36" s="4">
         <v>70</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D36" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C37" s="4">
         <v>82</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D37" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C38" s="4">
         <v>77</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D38" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C39" s="4">
         <v>72</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D39" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C40" s="4">
         <v>69</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D40" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C41" s="4">
         <v>83</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D41" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C42">
         <v>54</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D42" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C43">
         <v>66</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D43" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C44">
         <v>53</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D44" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C45">
         <v>54</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D45" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C46">
         <v>82</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D46" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C47">
         <v>86</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D47" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C48">
         <v>86</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D48" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C49">
         <v>76</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D49" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C50">
         <v>79</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D50" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C51">
         <v>78</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D51" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C52">
         <v>69</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D52" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C53">
         <v>76</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D53" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C54">
         <v>72</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D54" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C55">
         <v>75</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D55" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C56">
         <v>74</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D56" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C57">
         <v>94</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D57" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C58">
         <v>82</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D58" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C59">
         <v>54</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D59" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C60">
         <v>66</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D60" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C61">
         <v>53</v>
       </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D61" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C62">
         <v>54</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D62" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C63">
         <v>82</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D63" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C64">
         <v>86</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D64" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C65">
         <v>86</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D65" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C66">
         <v>76</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D66" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C67">
         <v>79</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D67" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C68">
         <v>78</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D68" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C69">
         <v>69</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D69" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C70">
         <v>76</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D70" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C71">
         <v>72</v>
       </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D71" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C72">
         <v>75</v>
       </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D72" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C73">
         <v>74</v>
       </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D73" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C74">
         <v>94</v>
       </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D74" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C75">
         <v>82</v>
       </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D75" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C76">
         <v>82</v>
       </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D76" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C77">
         <v>86</v>
       </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D77" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C78">
         <v>86</v>
       </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D78" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C79">
         <v>76</v>
       </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D79" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C80">
         <v>79</v>
       </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D80" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C81">
         <v>78</v>
       </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D81" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C82">
         <v>69</v>
       </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D82" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C83">
         <v>76</v>
       </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D83" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C84">
         <v>72</v>
       </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D84" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C85">
         <v>75</v>
       </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D85" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C86">
         <v>74</v>
       </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D86" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C87">
         <v>94</v>
       </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D87" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C88">
         <v>82</v>
       </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D88" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C89">
         <v>85</v>
       </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D89" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C90">
         <v>83</v>
       </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D90" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C91">
         <v>73</v>
       </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D91" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C92">
         <v>74</v>
       </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D92" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C93">
         <v>73</v>
       </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D93" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C94">
         <v>64</v>
       </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D94" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C95">
         <v>72</v>
       </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D95" s="5" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C96">
         <v>90</v>
       </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D96" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C97">
         <v>90</v>
       </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D97" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C98">
         <v>86</v>
       </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D98" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C99">
         <v>90</v>
       </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D99" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C100">
         <v>78</v>
       </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D100" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C101">
         <v>84</v>
       </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D101" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C102">
         <v>66</v>
       </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D102" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C103">
         <v>82</v>
       </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D103" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C104">
         <v>81</v>
       </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D104" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C105">
         <v>75</v>
       </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D105" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C106">
         <v>71</v>
       </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D106" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C107">
         <v>81</v>
       </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D107" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C108">
         <v>86</v>
       </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D108" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C109">
         <v>82</v>
       </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D109" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C110">
         <v>74</v>
       </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D110" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C111">
         <v>89</v>
       </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D111" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C112">
         <v>112</v>
       </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D112" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C113">
         <v>76</v>
       </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D113" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C114">
         <v>85</v>
       </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D114" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C115">
         <v>83</v>
       </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D115" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C116">
         <v>73</v>
       </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D116" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C117">
         <v>73</v>
       </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D117" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C118">
         <v>64</v>
       </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D118" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C119">
         <v>72</v>
       </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D119" s="5" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C120">
         <v>90</v>
       </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D120" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C121">
         <v>90</v>
       </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D121" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>72</v>
+        <v>124</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C122">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.2">
+        <v>90</v>
+      </c>
+      <c r="D122" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>125</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C123">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.2">
+        <v>78</v>
+      </c>
+      <c r="D123" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>126</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C124">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.2">
+        <v>84</v>
+      </c>
+      <c r="D124" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>127</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C125">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.2">
+        <v>66</v>
+      </c>
+      <c r="D125" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>128</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C126">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.2">
+        <v>71</v>
+      </c>
+      <c r="D126" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>129</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C127">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.2">
+        <v>81</v>
+      </c>
+      <c r="D127" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>130</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C128">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.2">
+        <v>86</v>
+      </c>
+      <c r="D128" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>131</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C129">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.2">
+        <v>82</v>
+      </c>
+      <c r="D129" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>132</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C130">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+      <c r="D130" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>133</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C131">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.2">
+        <v>89</v>
+      </c>
+      <c r="D131" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>134</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C132">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.2">
+        <v>112</v>
+      </c>
+      <c r="D132" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>135</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C133">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.2">
+        <v>76</v>
+      </c>
+      <c r="D133" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>136</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C134">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.2">
+        <v>83</v>
+      </c>
+      <c r="D134" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>137</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C135">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.2">
+        <v>73</v>
+      </c>
+      <c r="D135" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>138</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C136">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+      <c r="D136" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>139</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C137">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.2">
+        <v>73</v>
+      </c>
+      <c r="D137" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>140</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C138">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.2">
+        <v>64</v>
+      </c>
+      <c r="D138" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>141</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C139">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.2">
+        <v>72</v>
+      </c>
+      <c r="D139" s="5" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>142</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C140">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.2">
+        <v>90</v>
+      </c>
+      <c r="D140" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>143</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C141">
         <v>90</v>
       </c>
-    </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D141" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
-        <v>144</v>
+        <v>100</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C142">
         <v>90</v>
       </c>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D142" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>101</v>
+        <v>144</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C143">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.2">
+        <v>78</v>
+      </c>
+      <c r="D143" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>145</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C144">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.2">
+        <v>84</v>
+      </c>
+      <c r="D144" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>146</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C145">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.2">
+        <v>66</v>
+      </c>
+      <c r="D145" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>147</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C146">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.2">
+        <v>82</v>
+      </c>
+      <c r="D146" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>148</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C147">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.2">
+        <v>75</v>
+      </c>
+      <c r="D147" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>149</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C148">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.2">
+        <v>71</v>
+      </c>
+      <c r="D148" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>150</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C149">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.2">
+        <v>81</v>
+      </c>
+      <c r="D149" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>151</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C150">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.2">
+        <v>86</v>
+      </c>
+      <c r="D150" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>152</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C151">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.2">
+        <v>82</v>
+      </c>
+      <c r="D151" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>153</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C152">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+      <c r="D152" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>154</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C153">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.2">
+        <v>89</v>
+      </c>
+      <c r="D153" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>155</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C154">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.2">
+        <v>112</v>
+      </c>
+      <c r="D154" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>156</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C155">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.2">
+        <v>76</v>
+      </c>
+      <c r="D155" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>157</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C156">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.2">
+        <v>77</v>
+      </c>
+      <c r="D156" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>158</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C157">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.2">
+        <v>89</v>
+      </c>
+      <c r="D157" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>159</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C158">
         <v>89</v>
       </c>
-    </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D158" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>160</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C159">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+      <c r="D159" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>161</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C160">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.2">
+        <v>78</v>
+      </c>
+      <c r="D160" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>162</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C161">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.2">
+        <v>86</v>
+      </c>
+      <c r="D161" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>163</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C162">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.2">
+        <v>89</v>
+      </c>
+      <c r="D162" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>164</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C163">
         <v>89</v>
       </c>
-    </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D163" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>165</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C164">
         <v>89</v>
       </c>
-    </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D164" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>166</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C165">
         <v>89</v>
       </c>
-    </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D165" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>167</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C166">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.2">
+        <v>77</v>
+      </c>
+      <c r="D166" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>168</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C167">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.2">
+        <v>78</v>
+      </c>
+      <c r="D167" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>169</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C168">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.2">
+        <v>60</v>
+      </c>
+      <c r="D168" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>170</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C169">
         <v>60</v>
       </c>
-    </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D169" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>171</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C170">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+      <c r="D170" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>172</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C171">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A172" t="s">
-        <v>173</v>
-      </c>
-      <c r="B172" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C172">
         <v>86</v>
+      </c>
+      <c r="D171" t="s">
+        <v>172</v>
       </c>
     </row>
   </sheetData>
